--- a/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
@@ -308,6 +308,90 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="008300"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$G$2:$G$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A3AA7"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$H$2:$H$6</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E34948"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$6</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$I$2:$I$6</f>
+            </numRef>
+          </val>
+        </ser>
         <gapWidth val="30"/>
         <overlap val="100"/>
         <axId val="10"/>
@@ -396,7 +480,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -918,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -937,22 +1021,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Wind</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Solar</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Oil</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Coal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nuclear &amp; other</t>
         </is>
       </c>
     </row>
@@ -964,16 +1063,25 @@
         <v>1.538</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>1.51634</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.26651</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1.17666</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.41642</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -984,16 +1092,25 @@
         <v>1.538</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>1.51634</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.28046</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.17666</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.41722</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1004,16 +1121,25 @@
         <v>1.538</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>1.51633</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.30056</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>1.17666</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.73122</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1024,16 +1150,25 @@
         <v>1.538</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>1.51633</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.33617</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1.17666</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.73122</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1044,16 +1179,25 @@
         <v>1.538</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>1.51633</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.34438</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1.17666</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.73122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -826,7 +827,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -841,7 +841,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -863,7 +862,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -927,7 +925,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -1056,7 +1053,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1085,7 +1082,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1114,7 +1111,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1143,7 +1140,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1172,7 +1169,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">

--- a/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -158,7 +157,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Uruguay installed generation capacity (MIEM / DNE) (to 2025)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Uruguay installed generation capacity (MIEM / DNE) (to 2026)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$6</f>
+              <f>'Chart'!$B$2:$B$7</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$6</f>
+              <f>'Chart'!$C$2:$C$7</f>
             </numRef>
           </val>
         </ser>
@@ -244,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$6</f>
+              <f>'Chart'!$D$2:$D$7</f>
             </numRef>
           </val>
         </ser>
@@ -272,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$6</f>
+              <f>'Chart'!$E$2:$E$7</f>
             </numRef>
           </val>
         </ser>
@@ -291,7 +291,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -300,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$6</f>
+              <f>'Chart'!$F$2:$F$7</f>
             </numRef>
           </val>
         </ser>
@@ -319,7 +319,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -328,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$6</f>
+              <f>'Chart'!$G$2:$G$7</f>
             </numRef>
           </val>
         </ser>
@@ -347,7 +347,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -356,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$6</f>
+              <f>'Chart'!$H$2:$H$7</f>
             </numRef>
           </val>
         </ser>
@@ -375,7 +375,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -384,12 +384,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$6</f>
+              <f>'Chart'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$6</f>
+              <f>'Chart'!$I$2:$I$7</f>
             </numRef>
           </val>
         </ser>
@@ -827,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -837,10 +838,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2021 to 2025 (5 years), from 2021. MIEM's national series (UTE, private and mixed plants; private generators' backup sets excluded per MIEM's notes). Salto Grande counted at Uruguay's 50% share (MIEM note: 50% of 1,890 MW).</t>
-        </is>
-      </c>
-    </row>
+          <t>2021 to 2026 (6 years), from 2021. MIEM's national series (UTE, private and mixed plants; private generators' backup sets excluded per MIEM's notes). Salto Grande counted at Uruguay's 50% share (MIEM note: 50% of 1,890 MW).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -851,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MIEM / DNE (Direccion Nacional de Energia), 'Series estadisticas de energia electrica' - 'Potencia instalada por central' (https://www.gub.uy/ministerio-industria-energia-mineria/sites/ministerio-industria-energia-mineria/files/2026-06/Potencia%20instalada%20por%20central.zip), sheet 'Pot Inst Fuente'. Page: https://www.gub.uy/ministerio-industria-energia-mineria/datos-y-estadisticas/datos/series-estadisticas-energia-electrica. Data: UTE / elaboracion propia DNE.</t>
+          <t>MIEM / DNE (Direccion Nacional de Energia), 'Series estadisticas de energia electrica' - 'Potencia instalada por central' (https://www.gub.uy/ministerio-industria-energia-mineria/sites/ministerio-industria-energia-mineria/files/2026-10/Potencia%20instalada%20por%20central.zip), sheet 'Pot Inst Fuente'. Page: https://www.gub.uy/ministerio-industria-energia-mineria/datos-y-estadisticas/datos/series-estadisticas-energia-electrica. Data: UTE / elaboracion propia DNE.</t>
         </is>
       </c>
     </row>
@@ -862,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -925,6 +928,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -935,7 +939,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Latest row here (2025-01) vs Ember yearly capacity 2025 (GW; diff = (ours - Ember) / Ember):</t>
+          <t>Latest row here (2026-01) vs Ember yearly capacity 2025 (GW; diff = (ours - Ember) / Ember):</t>
         </is>
       </c>
     </row>
@@ -963,7 +967,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Solar: 0.344 GW here vs 0.340 GW Ember -&gt; +1.3%</t>
+          <t xml:space="preserve">  Solar: 0.348 GW here vs 0.340 GW Ember -&gt; +2.5%</t>
         </is>
       </c>
     </row>
@@ -984,7 +988,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Total: 5.307 GW here vs 5.320 GW Ember -&gt; -0.3%</t>
+          <t xml:space="preserve">  Total: 5.311 GW here vs 5.320 GW Ember -&gt; -0.2%</t>
         </is>
       </c>
     </row>
@@ -999,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1053,7 +1057,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1066,7 +1070,7 @@
         <v>1.51634</v>
       </c>
       <c r="E2" t="n">
-        <v>0.26651</v>
+        <v>0.26639</v>
       </c>
       <c r="F2" t="n">
         <v>1.17666</v>
@@ -1082,7 +1086,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1095,7 +1099,7 @@
         <v>1.51634</v>
       </c>
       <c r="E3" t="n">
-        <v>0.28046</v>
+        <v>0.28016</v>
       </c>
       <c r="F3" t="n">
         <v>1.17666</v>
@@ -1111,7 +1115,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1124,7 +1128,7 @@
         <v>1.51633</v>
       </c>
       <c r="E4" t="n">
-        <v>0.30056</v>
+        <v>0.30027</v>
       </c>
       <c r="F4" t="n">
         <v>1.17666</v>
@@ -1140,7 +1144,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1153,7 +1157,7 @@
         <v>1.51633</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33617</v>
+        <v>0.33577</v>
       </c>
       <c r="F5" t="n">
         <v>1.17666</v>
@@ -1169,7 +1173,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
@@ -1194,6 +1198,35 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.51633</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.17666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.73122</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1209,7 +1242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,7 +1316,7 @@
         <v>1516.34</v>
       </c>
       <c r="E2" t="n">
-        <v>266.51</v>
+        <v>266.39</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1301,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>4913.93</v>
+        <v>4913.81</v>
       </c>
     </row>
     <row r="3">
@@ -1318,7 +1351,7 @@
         <v>1516.34</v>
       </c>
       <c r="E3" t="n">
-        <v>280.46</v>
+        <v>280.16</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1336,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4928.68</v>
+        <v>4928.38</v>
       </c>
     </row>
     <row r="4">
@@ -1353,7 +1386,7 @@
         <v>1516.33</v>
       </c>
       <c r="E4" t="n">
-        <v>300.56</v>
+        <v>300.27</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1371,7 +1404,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>5262.77</v>
+        <v>5262.48</v>
       </c>
     </row>
     <row r="5">
@@ -1388,7 +1421,7 @@
         <v>1516.33</v>
       </c>
       <c r="E5" t="n">
-        <v>336.17</v>
+        <v>335.77</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1406,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5298.38</v>
+        <v>5297.98</v>
       </c>
     </row>
     <row r="6">
@@ -1442,6 +1475,41 @@
       </c>
       <c r="K6" t="n">
         <v>5306.59</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1538</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1516.33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>348.48</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1176.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>731.22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5310.69</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1612,11 @@
           <t>2025.0</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026.0</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1600,6 +1673,9 @@
       <c r="Q3" t="n">
         <v>180</v>
       </c>
+      <c r="R3" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1655,6 +1731,9 @@
       <c r="Q4" t="n">
         <v>925.7</v>
       </c>
+      <c r="R4" t="n">
+        <v>925.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1710,6 +1789,9 @@
       <c r="Q5" t="n">
         <v>70.95999999999999</v>
       </c>
+      <c r="R5" t="n">
+        <v>70.95999999999999</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1765,6 +1847,9 @@
       <c r="Q6" t="n">
         <v>1176.66</v>
       </c>
+      <c r="R6" t="n">
+        <v>1176.66</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1827,6 +1912,9 @@
       <c r="Q8" t="n">
         <v>728.6</v>
       </c>
+      <c r="R8" t="n">
+        <v>728.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1882,6 +1970,9 @@
       <c r="Q9" t="n">
         <v>2.62</v>
       </c>
+      <c r="R9" t="n">
+        <v>2.62</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1937,6 +2028,9 @@
       <c r="Q10" t="n">
         <v>731.22</v>
       </c>
+      <c r="R10" t="n">
+        <v>731.22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1999,6 +2093,9 @@
       <c r="Q12" t="n">
         <v>1538</v>
       </c>
+      <c r="R12" t="n">
+        <v>1538</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2054,6 +2151,9 @@
       <c r="Q13" t="n">
         <v>1538</v>
       </c>
+      <c r="R13" t="n">
+        <v>1538</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2116,6 +2216,9 @@
       <c r="Q15" t="n">
         <v>1516.3289</v>
       </c>
+      <c r="R15" t="n">
+        <v>1516.3289</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2171,6 +2274,9 @@
       <c r="Q16" t="n">
         <v>1516.3289</v>
       </c>
+      <c r="R16" t="n">
+        <v>1516.3289</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2219,20 +2325,23 @@
         <v>257.9428187999999</v>
       </c>
       <c r="M18" t="n">
-        <v>266.5062237999999</v>
+        <v>266.3862237999999</v>
       </c>
       <c r="N18" t="n">
-        <v>280.4577638000001</v>
+        <v>280.1593638000001</v>
       </c>
       <c r="O18" t="n">
-        <v>300.5637448</v>
+        <v>300.2653448</v>
       </c>
       <c r="P18" t="n">
-        <v>336.1723867999999</v>
+        <v>335.7689867999999</v>
       </c>
       <c r="Q18" t="n">
         <v>344.3787178</v>
       </c>
+      <c r="R18" t="n">
+        <v>348.4774628</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2274,20 +2383,23 @@
         <v>257.9428187999999</v>
       </c>
       <c r="M19" t="n">
-        <v>266.5062237999999</v>
+        <v>266.3862237999999</v>
       </c>
       <c r="N19" t="n">
-        <v>280.4577638000001</v>
+        <v>280.1593638000001</v>
       </c>
       <c r="O19" t="n">
-        <v>300.5637448</v>
+        <v>300.2653448</v>
       </c>
       <c r="P19" t="n">
-        <v>336.1723867999999</v>
+        <v>335.7689867999999</v>
       </c>
       <c r="Q19" t="n">
         <v>344.3787178</v>
       </c>
+      <c r="R19" t="n">
+        <v>348.4774628</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2296,7 +2408,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2690.0297949</v>
+        <v>2680.0297949</v>
       </c>
       <c r="C20" t="n">
         <v>2700.781134</v>
@@ -2329,19 +2441,22 @@
         <v>4905.2103188</v>
       </c>
       <c r="M20" t="n">
-        <v>4913.9237238</v>
+        <v>4913.8037238</v>
       </c>
       <c r="N20" t="n">
-        <v>4928.6776638</v>
+        <v>4928.3792638</v>
       </c>
       <c r="O20" t="n">
-        <v>5262.772644799999</v>
+        <v>5262.4742448</v>
       </c>
       <c r="P20" t="n">
-        <v>5298.3812868</v>
+        <v>5297.977886799999</v>
       </c>
       <c r="Q20" t="n">
         <v>5306.5876178</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5310.686362799999</v>
       </c>
     </row>
   </sheetData>
@@ -2355,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:M129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2534,11 @@
           <t>2025</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2484,6 +2604,9 @@
       <c r="L6" t="n">
         <v>180</v>
       </c>
+      <c r="M6" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2524,6 +2647,9 @@
       <c r="L7" t="n">
         <v>161</v>
       </c>
+      <c r="M7" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2540,6 +2666,9 @@
       <c r="L8" t="n">
         <v>314</v>
       </c>
+      <c r="M8" t="n">
+        <v>314</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2580,6 +2709,9 @@
       <c r="L9" t="n">
         <v>10</v>
       </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2620,6 +2752,9 @@
       <c r="L10" t="n">
         <v>5</v>
       </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2660,6 +2795,9 @@
       <c r="L11" t="n">
         <v>14</v>
       </c>
+      <c r="M11" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2700,6 +2838,9 @@
       <c r="L12" t="n">
         <v>10</v>
       </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2740,6 +2881,9 @@
       <c r="L13" t="n">
         <v>12</v>
       </c>
+      <c r="M13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2780,6 +2924,9 @@
       <c r="L14" t="n">
         <v>12</v>
       </c>
+      <c r="M14" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2820,6 +2967,9 @@
       <c r="L15" t="n">
         <v>7.5</v>
       </c>
+      <c r="M15" t="n">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2860,6 +3010,9 @@
       <c r="L16" t="n">
         <v>180</v>
       </c>
+      <c r="M16" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2913,6 +3066,9 @@
       <c r="L18" t="n">
         <v>3.1</v>
       </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2988,6 +3144,9 @@
       <c r="L24" t="n">
         <v>212</v>
       </c>
+      <c r="M24" t="n">
+        <v>212</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3028,6 +3187,9 @@
       <c r="L25" t="n">
         <v>300</v>
       </c>
+      <c r="M25" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3062,6 +3224,9 @@
       <c r="L26" t="n">
         <v>180</v>
       </c>
+      <c r="M26" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3093,6 +3258,9 @@
       <c r="L27" t="n">
         <v>180</v>
       </c>
+      <c r="M27" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3143,6 +3311,9 @@
       <c r="L29" t="n">
         <v>50</v>
       </c>
+      <c r="M29" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3193,6 +3364,9 @@
       <c r="L31" t="n">
         <v>3.7</v>
       </c>
+      <c r="M31" t="n">
+        <v>3.7</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3240,6 +3414,9 @@
       <c r="L33" t="n">
         <v>70</v>
       </c>
+      <c r="M33" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3294,6 +3471,9 @@
       <c r="L36" t="n">
         <v>0.96</v>
       </c>
+      <c r="M36" t="n">
+        <v>0.96</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3341,6 +3521,9 @@
       <c r="L38" t="n">
         <v>1</v>
       </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3388,6 +3571,9 @@
       <c r="L40" t="n">
         <v>0.6</v>
       </c>
+      <c r="M40" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3407,6 +3593,9 @@
       <c r="L41" t="n">
         <v>0.8</v>
       </c>
+      <c r="M41" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3435,6 +3624,9 @@
       <c r="L42" t="n">
         <v>0.22</v>
       </c>
+      <c r="M42" t="n">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3475,6 +3667,9 @@
       <c r="L43" t="n">
         <v>1907.88</v>
       </c>
+      <c r="M43" t="n">
+        <v>1907.88</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3522,6 +3717,9 @@
       <c r="L45" t="n">
         <v>152</v>
       </c>
+      <c r="M45" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3562,6 +3760,9 @@
       <c r="L46" t="n">
         <v>108</v>
       </c>
+      <c r="M46" t="n">
+        <v>108</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3602,6 +3803,9 @@
       <c r="L47" t="n">
         <v>333</v>
       </c>
+      <c r="M47" t="n">
+        <v>333</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3642,6 +3846,9 @@
       <c r="L48" t="n">
         <v>945</v>
       </c>
+      <c r="M48" t="n">
+        <v>945</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3682,6 +3889,9 @@
       <c r="L49" t="n">
         <v>1538</v>
       </c>
+      <c r="M49" t="n">
+        <v>1538</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3751,6 +3961,9 @@
       <c r="L52" t="n">
         <v>10</v>
       </c>
+      <c r="M52" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3791,6 +4004,9 @@
       <c r="L53" t="n">
         <v>10</v>
       </c>
+      <c r="M53" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3831,6 +4047,9 @@
       <c r="L54" t="n">
         <v>2.95</v>
       </c>
+      <c r="M54" t="n">
+        <v>2.95</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3871,6 +4090,9 @@
       <c r="L55" t="n">
         <v>18</v>
       </c>
+      <c r="M55" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3911,6 +4133,9 @@
       <c r="L56" t="n">
         <v>17.2</v>
       </c>
+      <c r="M56" t="n">
+        <v>17.2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3951,6 +4176,9 @@
       <c r="L57" t="n">
         <v>1.8</v>
       </c>
+      <c r="M57" t="n">
+        <v>1.8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3991,6 +4219,9 @@
       <c r="L58" t="n">
         <v>3.6</v>
       </c>
+      <c r="M58" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4031,6 +4262,9 @@
       <c r="L59" t="n">
         <v>50</v>
       </c>
+      <c r="M59" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4071,6 +4305,9 @@
       <c r="L60" t="n">
         <v>50</v>
       </c>
+      <c r="M60" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4111,6 +4348,9 @@
       <c r="L61" t="n">
         <v>50</v>
       </c>
+      <c r="M61" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4151,6 +4391,9 @@
       <c r="L62" t="n">
         <v>42</v>
       </c>
+      <c r="M62" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4191,6 +4434,9 @@
       <c r="L63" t="n">
         <v>7.74</v>
       </c>
+      <c r="M63" t="n">
+        <v>7.74</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4231,6 +4477,9 @@
       <c r="L64" t="n">
         <v>18</v>
       </c>
+      <c r="M64" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4271,6 +4520,9 @@
       <c r="L65" t="n">
         <v>20</v>
       </c>
+      <c r="M65" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4311,6 +4563,9 @@
       <c r="L66" t="n">
         <v>50</v>
       </c>
+      <c r="M66" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4351,6 +4606,9 @@
       <c r="L67" t="n">
         <v>67.2</v>
       </c>
+      <c r="M67" t="n">
+        <v>67.2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4391,6 +4649,9 @@
       <c r="L68" t="n">
         <v>65.09999999999999</v>
       </c>
+      <c r="M68" t="n">
+        <v>65.09999999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4431,6 +4692,9 @@
       <c r="L69" t="n">
         <v>50</v>
       </c>
+      <c r="M69" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4471,6 +4735,9 @@
       <c r="L70" t="n">
         <v>50</v>
       </c>
+      <c r="M70" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4511,6 +4778,9 @@
       <c r="L71" t="n">
         <v>58.75</v>
       </c>
+      <c r="M71" t="n">
+        <v>58.75</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4551,6 +4821,9 @@
       <c r="L72" t="n">
         <v>58.75</v>
       </c>
+      <c r="M72" t="n">
+        <v>58.75</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4591,6 +4864,9 @@
       <c r="L73" t="n">
         <v>50</v>
       </c>
+      <c r="M73" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4631,6 +4907,9 @@
       <c r="L74" t="n">
         <v>40</v>
       </c>
+      <c r="M74" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4671,6 +4950,9 @@
       <c r="L75" t="n">
         <v>50</v>
       </c>
+      <c r="M75" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4711,6 +4993,9 @@
       <c r="L76" t="n">
         <v>9</v>
       </c>
+      <c r="M76" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4751,6 +5036,9 @@
       <c r="L77" t="n">
         <v>10</v>
       </c>
+      <c r="M77" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4788,6 +5076,9 @@
       <c r="L78" t="n">
         <v>3.6</v>
       </c>
+      <c r="M78" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4825,6 +5116,9 @@
       <c r="L79" t="n">
         <v>10</v>
       </c>
+      <c r="M79" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4862,6 +5156,9 @@
       <c r="L80" t="n">
         <v>50</v>
       </c>
+      <c r="M80" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4899,6 +5196,9 @@
       <c r="L81" t="n">
         <v>49.5</v>
       </c>
+      <c r="M81" t="n">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4936,6 +5236,9 @@
       <c r="L82" t="n">
         <v>141.6</v>
       </c>
+      <c r="M82" t="n">
+        <v>141.6</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4973,6 +5276,9 @@
       <c r="L83" t="n">
         <v>70</v>
       </c>
+      <c r="M83" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5010,6 +5316,9 @@
       <c r="L84" t="n">
         <v>10</v>
       </c>
+      <c r="M84" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5047,6 +5356,9 @@
       <c r="L85" t="n">
         <v>10</v>
       </c>
+      <c r="M85" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5084,6 +5396,9 @@
       <c r="L86" t="n">
         <v>10</v>
       </c>
+      <c r="M86" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5118,6 +5433,9 @@
       <c r="L87" t="n">
         <v>49.2</v>
       </c>
+      <c r="M87" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5152,6 +5470,9 @@
       <c r="L88" t="n">
         <v>70</v>
       </c>
+      <c r="M88" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5186,6 +5507,9 @@
       <c r="L89" t="n">
         <v>49.2</v>
       </c>
+      <c r="M89" t="n">
+        <v>49.2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5220,6 +5544,9 @@
       <c r="L90" t="n">
         <v>70</v>
       </c>
+      <c r="M90" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5254,6 +5581,9 @@
       <c r="L91" t="n">
         <v>2</v>
       </c>
+      <c r="M91" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5288,6 +5618,9 @@
       <c r="L92" t="n">
         <v>51.7</v>
       </c>
+      <c r="M92" t="n">
+        <v>51.7</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5322,6 +5655,9 @@
       <c r="L93" t="n">
         <v>2</v>
       </c>
+      <c r="M93" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5362,6 +5698,9 @@
       <c r="L94" t="n">
         <v>0.1389</v>
       </c>
+      <c r="M94" t="n">
+        <v>0.1389</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5396,6 +5735,9 @@
       <c r="L95" t="n">
         <v>7.3</v>
       </c>
+      <c r="M95" t="n">
+        <v>7.3</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5458,6 +5800,11 @@
           <t>s/d</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5498,6 +5845,9 @@
       <c r="L97" t="n">
         <v>1516.3289</v>
       </c>
+      <c r="M97" t="n">
+        <v>1516.3289</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5545,6 +5895,9 @@
       <c r="L99" t="n">
         <v>0.48</v>
       </c>
+      <c r="M99" t="n">
+        <v>0.48</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5585,6 +5938,9 @@
       <c r="L100" t="n">
         <v>50</v>
       </c>
+      <c r="M100" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5625,6 +5981,9 @@
       <c r="L101" t="n">
         <v>8</v>
       </c>
+      <c r="M101" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5662,6 +6021,9 @@
       <c r="L102" t="n">
         <v>20</v>
       </c>
+      <c r="M102" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5702,6 +6064,9 @@
       <c r="L103" t="n">
         <v>0.0522</v>
       </c>
+      <c r="M103" t="n">
+        <v>0.0522</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5736,6 +6101,9 @@
       <c r="L104" t="n">
         <v>1.75</v>
       </c>
+      <c r="M104" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5770,6 +6138,9 @@
       <c r="L105" t="n">
         <v>16</v>
       </c>
+      <c r="M105" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5804,6 +6175,9 @@
       <c r="L106" t="n">
         <v>9.5</v>
       </c>
+      <c r="M106" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5838,6 +6212,9 @@
       <c r="L107" t="n">
         <v>9.5</v>
       </c>
+      <c r="M107" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5872,6 +6249,9 @@
       <c r="L108" t="n">
         <v>50</v>
       </c>
+      <c r="M108" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5906,6 +6286,9 @@
       <c r="L109" t="n">
         <v>11.25</v>
       </c>
+      <c r="M109" t="n">
+        <v>11.25</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5940,6 +6323,9 @@
       <c r="L110" t="n">
         <v>9.5</v>
       </c>
+      <c r="M110" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5974,6 +6360,9 @@
       <c r="L111" t="n">
         <v>20</v>
       </c>
+      <c r="M111" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6008,6 +6397,9 @@
       <c r="L112" t="n">
         <v>9.5</v>
       </c>
+      <c r="M112" t="n">
+        <v>9.5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6042,6 +6434,9 @@
       <c r="L113" t="n">
         <v>10</v>
       </c>
+      <c r="M113" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6073,6 +6468,9 @@
       <c r="L114" t="n">
         <v>1</v>
       </c>
+      <c r="M114" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6104,6 +6502,9 @@
       <c r="L115" t="n">
         <v>1</v>
       </c>
+      <c r="M115" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6135,6 +6536,9 @@
       <c r="L116" t="n">
         <v>1</v>
       </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6160,6 +6564,9 @@
       <c r="L117" t="n">
         <v>0.25</v>
       </c>
+      <c r="M117" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6176,6 +6583,9 @@
       <c r="L118" t="n">
         <v>14</v>
       </c>
+      <c r="M118" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6189,6 +6599,9 @@
       <c r="L119" t="n">
         <v>26</v>
       </c>
+      <c r="M119" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6229,6 +6642,9 @@
       <c r="L120" t="n">
         <v>60.68570899999995</v>
       </c>
+      <c r="M120" t="n">
+        <v>63.38445399999996</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6255,19 +6671,22 @@
         <v>0.9972828</v>
       </c>
       <c r="H121" t="n">
-        <v>1.6087828</v>
+        <v>1.4887828</v>
       </c>
       <c r="I121" t="n">
-        <v>2.0721828</v>
+        <v>1.7737828</v>
       </c>
       <c r="J121" t="n">
-        <v>2.3559128</v>
+        <v>2.0575128</v>
       </c>
       <c r="K121" t="n">
-        <v>2.649912800000001</v>
+        <v>2.246512800000001</v>
       </c>
       <c r="L121" t="n">
-        <v>2.8748628</v>
+        <v>2.874862800000001</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2.874862800000001</v>
       </c>
     </row>
     <row r="122">
@@ -6309,6 +6728,9 @@
       <c r="L122" t="n">
         <v>0.310446</v>
       </c>
+      <c r="M122" t="n">
+        <v>0.310446</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6346,6 +6768,9 @@
       <c r="L123" t="n">
         <v>11.7255</v>
       </c>
+      <c r="M123" t="n">
+        <v>13.1255</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6372,20 +6797,23 @@
         <v>257.9428187999999</v>
       </c>
       <c r="H124" t="n">
-        <v>266.5062237999999</v>
+        <v>266.3862237999999</v>
       </c>
       <c r="I124" t="n">
-        <v>280.4577638000001</v>
+        <v>280.1593638000001</v>
       </c>
       <c r="J124" t="n">
-        <v>300.5637448</v>
+        <v>300.2653448</v>
       </c>
       <c r="K124" t="n">
-        <v>336.1723867999999</v>
+        <v>335.7689867999999</v>
       </c>
       <c r="L124" t="n">
         <v>344.3787178</v>
       </c>
+      <c r="M124" t="n">
+        <v>348.4774628</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6412,19 +6840,22 @@
         <v>4905.2103188</v>
       </c>
       <c r="H125" t="n">
-        <v>4913.9237238</v>
+        <v>4913.8037238</v>
       </c>
       <c r="I125" t="n">
-        <v>4928.6776638</v>
+        <v>4928.3792638</v>
       </c>
       <c r="J125" t="n">
-        <v>5262.772644799999</v>
+        <v>5262.4742448</v>
       </c>
       <c r="K125" t="n">
-        <v>5298.3812868</v>
+        <v>5297.977886799999</v>
       </c>
       <c r="L125" t="n">
         <v>5306.5876178</v>
+      </c>
+      <c r="M125" t="n">
+        <v>5310.686362799999</v>
       </c>
     </row>
     <row r="126">

--- a/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -827,7 +828,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,7 +842,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -864,7 +863,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -928,7 +926,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -1057,7 +1054,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1086,7 +1083,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1115,7 +1112,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1144,7 +1141,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1173,7 +1170,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
@@ -1202,7 +1199,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">

--- a/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/uruguay_power_capacity.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -828,6 +827,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -842,6 +842,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -863,6 +864,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
@@ -926,6 +928,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -1054,7 +1057,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1083,7 +1086,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B3" t="n">
@@ -1112,7 +1115,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B4" t="n">
@@ -1141,7 +1144,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B5" t="n">
@@ -1170,7 +1173,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B6" t="n">
@@ -1199,7 +1202,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
